--- a/Result/profitability/1513.xlsx
+++ b/Result/profitability/1513.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.39</v>
       </c>
       <c r="M2" t="n">
-        <v>1.74875</v>
+        <v>1.8375</v>
       </c>
       <c r="N2" t="n">
-        <v>24.76625</v>
+        <v>25.3175</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.4</v>
       </c>
       <c r="M3" t="n">
-        <v>1.56625</v>
+        <v>1.67125</v>
       </c>
       <c r="N3" t="n">
-        <v>23.86625</v>
+        <v>24.21625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.3</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3875</v>
+        <v>1.48625</v>
       </c>
       <c r="N4" t="n">
-        <v>22.935</v>
+        <v>23.31125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.06</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1575</v>
+        <v>1.24</v>
       </c>
       <c r="N5" t="n">
-        <v>21.045</v>
+        <v>21.515</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>0.955</v>
+        <v>0.98875</v>
       </c>
       <c r="N6" t="n">
-        <v>20.35625</v>
+        <v>20.6775</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>0.73875</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>19.94375</v>
+        <v>20.12375</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4875</v>
+        <v>0.5662499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>18.06375</v>
+        <v>18.37125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1513</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>7533</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5391</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2142</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28.44</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1510</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>20.05%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>89</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1600</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1268</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.02125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.88375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6299999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3247422680412371</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>2.460000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.09468822170900704</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.6599999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3455497382198953</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.760000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.1523500810372773</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
